--- a/output/curva_abc_reggae_6.xlsx
+++ b/output/curva_abc_reggae_6.xlsx
@@ -1043,21 +1043,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00D8F1DC"/>
+          <fgColor rgb="009FE3A5"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFF4CC"/>
+          <fgColor rgb="00FFE066"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FBD7D5"/>
+          <fgColor rgb="00FFB07A"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1246,25 +1246,22 @@
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
+      <areaChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🟢 Primeira'!U11</f>
+              <f>'🟢 Primeira'!AA11</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1FAE4D"/>
+              <a:srgbClr val="FFB07A"/>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="0E7A2E"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1275,7 +1272,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'🟢 Primeira'!$U$12:$U$21</f>
+              <f>'🟢 Primeira'!$AA$12:$AA$21</f>
             </numRef>
           </val>
         </ser>
@@ -1284,20 +1281,86 @@
           <order val="1"/>
           <tx>
             <strRef>
+              <f>'🟢 Primeira'!Z11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFE066"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$Q$12:$Q$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$Z$12:$Z$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'🟢 Primeira'!Y11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9FE3A5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$Q$12:$Q$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$Y$12:$Y$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
               <f>'🟢 Primeira'!V11</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="F4C81E"/>
+              <a:srgbClr val="3FB3E5"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="6000">
               <a:solidFill>
-                <a:srgbClr val="B89200"/>
+                <a:srgbClr val="1A78A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'🟢 Primeira'!$Q$12:$Q$21</f>
@@ -1310,8 +1373,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'🟢 Primeira'!W11</f>
@@ -1319,15 +1382,19 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D4322B"/>
+              <a:srgbClr val="3FB3E5"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="6000">
               <a:solidFill>
-                <a:srgbClr val="8A1F1A"/>
+                <a:srgbClr val="1A78A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'🟢 Primeira'!$Q$12:$Q$21</f>
@@ -1339,7 +1406,41 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'🟢 Primeira'!X11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3FB3E5"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="1A78A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'🟢 Primeira'!$Q$12:$Q$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟢 Primeira'!$X$12:$X$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1347,15 +1448,15 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
               <f>'🟢 Primeira'!T11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln w="44450">
               <a:solidFill>
                 <a:srgbClr val="C0392B"/>
               </a:solidFill>
@@ -1370,10 +1471,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dLbls>
-            <numFmt formatCode="0%"/>
-            <showVal val="1"/>
-          </dLbls>
           <val>
             <numRef>
               <f>'🟢 Primeira'!$T$12:$T$21</f>
@@ -1382,7 +1479,7 @@
           <smooth val="1"/>
         </ser>
         <axId val="10"/>
-        <axId val="200"/>
+        <axId val="100"/>
       </lineChart>
       <catAx>
         <axId val="10"/>
@@ -1390,21 +1487,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>SKU (ordenado por V.T.)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1414,64 +1496,18 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>V.T. (R$)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-      <valAx>
-        <axId val="200"/>
-        <scaling>
-          <orientation val="minMax"/>
           <max val="1"/>
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>% Acumulado</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="max"/>
         <majorUnit val="0.1"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1497,25 +1533,22 @@
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
+      <areaChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🟡 01'!U11</f>
+              <f>'🟡 01'!AA11</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1FAE4D"/>
+              <a:srgbClr val="FFB07A"/>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="0E7A2E"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1526,7 +1559,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'🟡 01'!$U$12:$U$31</f>
+              <f>'🟡 01'!$AA$12:$AA$31</f>
             </numRef>
           </val>
         </ser>
@@ -1535,20 +1568,86 @@
           <order val="1"/>
           <tx>
             <strRef>
+              <f>'🟡 01'!Z11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFE066"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$Q$12:$Q$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$Z$12:$Z$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'🟡 01'!Y11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9FE3A5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$Q$12:$Q$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$Y$12:$Y$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
               <f>'🟡 01'!V11</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="F4C81E"/>
+              <a:srgbClr val="3FB3E5"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="6000">
               <a:solidFill>
-                <a:srgbClr val="B89200"/>
+                <a:srgbClr val="1A78A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'🟡 01'!$Q$12:$Q$31</f>
@@ -1561,8 +1660,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'🟡 01'!W11</f>
@@ -1570,15 +1669,19 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D4322B"/>
+              <a:srgbClr val="3FB3E5"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="6000">
               <a:solidFill>
-                <a:srgbClr val="8A1F1A"/>
+                <a:srgbClr val="1A78A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'🟡 01'!$Q$12:$Q$31</f>
@@ -1590,7 +1693,41 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'🟡 01'!X11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3FB3E5"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="1A78A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'🟡 01'!$Q$12:$Q$31</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🟡 01'!$X$12:$X$31</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1598,15 +1735,15 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
               <f>'🟡 01'!T11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln w="44450">
               <a:solidFill>
                 <a:srgbClr val="C0392B"/>
               </a:solidFill>
@@ -1621,10 +1758,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dLbls>
-            <numFmt formatCode="0%"/>
-            <showVal val="1"/>
-          </dLbls>
           <val>
             <numRef>
               <f>'🟡 01'!$T$12:$T$31</f>
@@ -1633,7 +1766,7 @@
           <smooth val="1"/>
         </ser>
         <axId val="10"/>
-        <axId val="200"/>
+        <axId val="100"/>
       </lineChart>
       <catAx>
         <axId val="10"/>
@@ -1641,21 +1774,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>SKU (ordenado por V.T.)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1665,64 +1783,18 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>V.T. (R$)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-      <valAx>
-        <axId val="200"/>
-        <scaling>
-          <orientation val="minMax"/>
           <max val="1"/>
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>% Acumulado</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="max"/>
         <majorUnit val="0.1"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1748,25 +1820,22 @@
       </tx>
     </title>
     <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="stacked"/>
+      <areaChart>
+        <grouping val="standard"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🔴 02'!U11</f>
+              <f>'🔴 02'!AA11</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1FAE4D"/>
+              <a:srgbClr val="FFB07A"/>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="0E7A2E"/>
-              </a:solidFill>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1777,7 +1846,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'🔴 02'!$U$12:$U$41</f>
+              <f>'🔴 02'!$AA$12:$AA$41</f>
             </numRef>
           </val>
         </ser>
@@ -1786,20 +1855,86 @@
           <order val="1"/>
           <tx>
             <strRef>
+              <f>'🔴 02'!Z11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFE066"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$Q$12:$Q$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$Z$12:$Z$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'🔴 02'!Y11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9FE3A5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$Q$12:$Q$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$Y$12:$Y$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </areaChart>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
               <f>'🔴 02'!V11</f>
             </strRef>
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="F4C81E"/>
+              <a:srgbClr val="3FB3E5"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="6000">
               <a:solidFill>
-                <a:srgbClr val="B89200"/>
+                <a:srgbClr val="1A78A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'🔴 02'!$Q$12:$Q$41</f>
@@ -1812,8 +1947,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'🔴 02'!W11</f>
@@ -1821,15 +1956,19 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="D4322B"/>
+              <a:srgbClr val="3FB3E5"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="6000">
               <a:solidFill>
-                <a:srgbClr val="8A1F1A"/>
+                <a:srgbClr val="1A78A0"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
           <cat>
             <numRef>
               <f>'🔴 02'!$Q$12:$Q$41</f>
@@ -1841,7 +1980,41 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'🔴 02'!X11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="3FB3E5"/>
+            </a:solidFill>
+            <a:ln w="6000">
+              <a:solidFill>
+                <a:srgbClr val="1A78A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showSerName val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'🔴 02'!$Q$12:$Q$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'🔴 02'!$X$12:$X$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
         <overlap val="100"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1849,15 +2022,15 @@
       <lineChart>
         <grouping val="standard"/>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="6"/>
+          <order val="6"/>
           <tx>
             <strRef>
               <f>'🔴 02'!T11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28000">
+            <a:ln w="44450">
               <a:solidFill>
                 <a:srgbClr val="C0392B"/>
               </a:solidFill>
@@ -1872,10 +2045,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <dLbls>
-            <numFmt formatCode="0%"/>
-            <showVal val="1"/>
-          </dLbls>
           <val>
             <numRef>
               <f>'🔴 02'!$T$12:$T$41</f>
@@ -1884,7 +2053,7 @@
           <smooth val="1"/>
         </ser>
         <axId val="10"/>
-        <axId val="200"/>
+        <axId val="100"/>
       </lineChart>
       <catAx>
         <axId val="10"/>
@@ -1892,21 +2061,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>SKU (ordenado por V.T.)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
@@ -1916,64 +2070,18 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>V.T. (R$)</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-      <valAx>
-        <axId val="200"/>
-        <scaling>
-          <orientation val="minMax"/>
           <max val="1"/>
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>% Acumulado</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
+        <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="max"/>
         <majorUnit val="0.1"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -2127,7 +2235,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="3960000"/>
+    <ext cx="10080000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2154,7 +2262,7 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="3960000"/>
+    <ext cx="10080000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2181,7 +2289,7 @@
       <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9360000" cy="3960000"/>
+    <ext cx="10080000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2999,7 +3107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3016,15 +3124,19 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="12" customWidth="1" min="16" max="16"/>
-    <col hidden="1" width="12" customWidth="1" min="17" max="17"/>
-    <col hidden="1" width="12" customWidth="1" min="18" max="18"/>
-    <col hidden="1" width="12" customWidth="1" min="19" max="19"/>
-    <col hidden="1" width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="11" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="11" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="11" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="11" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
@@ -3328,20 +3440,40 @@
       </c>
       <c r="U11" s="97" t="inlineStr">
         <is>
-          <t>Classe A</t>
+          <t>% Individual</t>
         </is>
       </c>
       <c r="V11" s="97" t="inlineStr">
         <is>
-          <t>Classe B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="W11" s="97" t="inlineStr">
         <is>
-          <t>Classe C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X11" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y11" s="97" t="inlineStr">
+        <is>
+          <t>Banda A</t>
+        </is>
+      </c>
+      <c r="Z11" s="97" t="inlineStr">
+        <is>
+          <t>Banda B</t>
+        </is>
+      </c>
+      <c r="AA11" s="97" t="inlineStr">
+        <is>
+          <t>Banda C</t>
+        </is>
+      </c>
+      <c r="AB11" s="97" t="inlineStr">
         <is>
           <t>score</t>
         </is>
@@ -3387,11 +3519,11 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P12),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P12),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R12" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P12),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P12),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S12">
@@ -3402,19 +3534,35 @@
         <f>IFERROR($R12/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U12" s="99">
-        <f>IF($S12="A",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="V12" s="99">
-        <f>IF($S12="B",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="W12" s="99">
-        <f>IF($S12="C",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="X12">
+      <c r="U12" s="100">
+        <f>IFERROR($R12/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="100">
+        <f>IF($S12="A",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="W12" s="100">
+        <f>IF($S12="B",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="X12" s="100">
+        <f>IF($S12="C",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="Y12" s="100">
+        <f>IF($S12="A",$T12,NA())</f>
+        <v/>
+      </c>
+      <c r="Z12" s="100">
+        <f>IF(OR($S12="A",$S12="B"),$T12,NA())</f>
+        <v/>
+      </c>
+      <c r="AA12" s="100">
+        <f>$T12</f>
+        <v/>
+      </c>
+      <c r="AB12">
         <f>IFERROR($G12+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3459,11 +3607,11 @@
         <v>2</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P13),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P13),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R13" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P13),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P13),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S13">
@@ -3474,19 +3622,35 @@
         <f>IFERROR($T12+$R13/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U13" s="99">
-        <f>IF($S13="A",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="V13" s="99">
-        <f>IF($S13="B",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="W13" s="99">
-        <f>IF($S13="C",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="X13">
+      <c r="U13" s="100">
+        <f>IFERROR($R13/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V13" s="100">
+        <f>IF($S13="A",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="W13" s="100">
+        <f>IF($S13="B",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="X13" s="100">
+        <f>IF($S13="C",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="Y13" s="100">
+        <f>IF($S13="A",$T13,NA())</f>
+        <v/>
+      </c>
+      <c r="Z13" s="100">
+        <f>IF(OR($S13="A",$S13="B"),$T13,NA())</f>
+        <v/>
+      </c>
+      <c r="AA13" s="100">
+        <f>$T13</f>
+        <v/>
+      </c>
+      <c r="AB13">
         <f>IFERROR($G13+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3531,11 +3695,11 @@
         <v>3</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P14),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P14),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R14" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P14),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P14),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S14">
@@ -3546,19 +3710,35 @@
         <f>IFERROR($T13+$R14/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U14" s="99">
-        <f>IF($S14="A",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="V14" s="99">
-        <f>IF($S14="B",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="W14" s="99">
-        <f>IF($S14="C",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="X14">
+      <c r="U14" s="100">
+        <f>IFERROR($R14/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="100">
+        <f>IF($S14="A",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="W14" s="100">
+        <f>IF($S14="B",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="X14" s="100">
+        <f>IF($S14="C",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="Y14" s="100">
+        <f>IF($S14="A",$T14,NA())</f>
+        <v/>
+      </c>
+      <c r="Z14" s="100">
+        <f>IF(OR($S14="A",$S14="B"),$T14,NA())</f>
+        <v/>
+      </c>
+      <c r="AA14" s="100">
+        <f>$T14</f>
+        <v/>
+      </c>
+      <c r="AB14">
         <f>IFERROR($G14+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3603,11 +3783,11 @@
         <v>4</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P15),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P15),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R15" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P15),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P15),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S15">
@@ -3618,19 +3798,35 @@
         <f>IFERROR($T14+$R15/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U15" s="99">
-        <f>IF($S15="A",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="V15" s="99">
-        <f>IF($S15="B",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="W15" s="99">
-        <f>IF($S15="C",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="X15">
+      <c r="U15" s="100">
+        <f>IFERROR($R15/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="100">
+        <f>IF($S15="A",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="W15" s="100">
+        <f>IF($S15="B",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="X15" s="100">
+        <f>IF($S15="C",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="Y15" s="100">
+        <f>IF($S15="A",$T15,NA())</f>
+        <v/>
+      </c>
+      <c r="Z15" s="100">
+        <f>IF(OR($S15="A",$S15="B"),$T15,NA())</f>
+        <v/>
+      </c>
+      <c r="AA15" s="100">
+        <f>$T15</f>
+        <v/>
+      </c>
+      <c r="AB15">
         <f>IFERROR($G15+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3675,11 +3871,11 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P16),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P16),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R16" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P16),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P16),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S16">
@@ -3690,19 +3886,35 @@
         <f>IFERROR($T15+$R16/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U16" s="99">
-        <f>IF($S16="A",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="V16" s="99">
-        <f>IF($S16="B",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="W16" s="99">
-        <f>IF($S16="C",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="X16">
+      <c r="U16" s="100">
+        <f>IFERROR($R16/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="100">
+        <f>IF($S16="A",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="W16" s="100">
+        <f>IF($S16="B",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="X16" s="100">
+        <f>IF($S16="C",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="Y16" s="100">
+        <f>IF($S16="A",$T16,NA())</f>
+        <v/>
+      </c>
+      <c r="Z16" s="100">
+        <f>IF(OR($S16="A",$S16="B"),$T16,NA())</f>
+        <v/>
+      </c>
+      <c r="AA16" s="100">
+        <f>$T16</f>
+        <v/>
+      </c>
+      <c r="AB16">
         <f>IFERROR($G16+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3747,11 +3959,11 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P17),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P17),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R17" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P17),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P17),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S17">
@@ -3762,19 +3974,35 @@
         <f>IFERROR($T16+$R17/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U17" s="99">
-        <f>IF($S17="A",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="V17" s="99">
-        <f>IF($S17="B",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="W17" s="99">
-        <f>IF($S17="C",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="X17">
+      <c r="U17" s="100">
+        <f>IFERROR($R17/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="100">
+        <f>IF($S17="A",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="W17" s="100">
+        <f>IF($S17="B",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="X17" s="100">
+        <f>IF($S17="C",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="Y17" s="100">
+        <f>IF($S17="A",$T17,NA())</f>
+        <v/>
+      </c>
+      <c r="Z17" s="100">
+        <f>IF(OR($S17="A",$S17="B"),$T17,NA())</f>
+        <v/>
+      </c>
+      <c r="AA17" s="100">
+        <f>$T17</f>
+        <v/>
+      </c>
+      <c r="AB17">
         <f>IFERROR($G17+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3819,11 +4047,11 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P18),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P18),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R18" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P18),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P18),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S18">
@@ -3834,19 +4062,35 @@
         <f>IFERROR($T17+$R18/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U18" s="99">
-        <f>IF($S18="A",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="V18" s="99">
-        <f>IF($S18="B",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="W18" s="99">
-        <f>IF($S18="C",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="X18">
+      <c r="U18" s="100">
+        <f>IFERROR($R18/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V18" s="100">
+        <f>IF($S18="A",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="W18" s="100">
+        <f>IF($S18="B",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="X18" s="100">
+        <f>IF($S18="C",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="Y18" s="100">
+        <f>IF($S18="A",$T18,NA())</f>
+        <v/>
+      </c>
+      <c r="Z18" s="100">
+        <f>IF(OR($S18="A",$S18="B"),$T18,NA())</f>
+        <v/>
+      </c>
+      <c r="AA18" s="100">
+        <f>$T18</f>
+        <v/>
+      </c>
+      <c r="AB18">
         <f>IFERROR($G18+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3891,11 +4135,11 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P19),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P19),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R19" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P19),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P19),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S19">
@@ -3906,19 +4150,35 @@
         <f>IFERROR($T18+$R19/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U19" s="99">
-        <f>IF($S19="A",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="V19" s="99">
-        <f>IF($S19="B",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="W19" s="99">
-        <f>IF($S19="C",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="X19">
+      <c r="U19" s="100">
+        <f>IFERROR($R19/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V19" s="100">
+        <f>IF($S19="A",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="W19" s="100">
+        <f>IF($S19="B",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="X19" s="100">
+        <f>IF($S19="C",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="Y19" s="100">
+        <f>IF($S19="A",$T19,NA())</f>
+        <v/>
+      </c>
+      <c r="Z19" s="100">
+        <f>IF(OR($S19="A",$S19="B"),$T19,NA())</f>
+        <v/>
+      </c>
+      <c r="AA19" s="100">
+        <f>$T19</f>
+        <v/>
+      </c>
+      <c r="AB19">
         <f>IFERROR($G19+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -3963,11 +4223,11 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P20),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P20),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R20" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P20),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P20),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S20">
@@ -3978,19 +4238,35 @@
         <f>IFERROR($T19+$R20/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U20" s="99">
-        <f>IF($S20="A",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="V20" s="99">
-        <f>IF($S20="B",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="W20" s="99">
-        <f>IF($S20="C",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="X20">
+      <c r="U20" s="100">
+        <f>IFERROR($R20/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="100">
+        <f>IF($S20="A",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="W20" s="100">
+        <f>IF($S20="B",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="X20" s="100">
+        <f>IF($S20="C",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="Y20" s="100">
+        <f>IF($S20="A",$T20,NA())</f>
+        <v/>
+      </c>
+      <c r="Z20" s="100">
+        <f>IF(OR($S20="A",$S20="B"),$T20,NA())</f>
+        <v/>
+      </c>
+      <c r="AA20" s="100">
+        <f>$T20</f>
+        <v/>
+      </c>
+      <c r="AB20">
         <f>IFERROR($G20+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4035,11 +4311,11 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($X$12:$X$21,$P21),$X$12:$X$21,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$21,MATCH(LARGE($AB$12:$AB$21,$P21),$AB$12:$AB$21,0)),"")</f>
         <v/>
       </c>
       <c r="R21" s="99">
-        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($X$12:$X$21,$P21),$X$12:$X$21,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$21,MATCH(LARGE($AB$12:$AB$21,$P21),$AB$12:$AB$21,0)),0)</f>
         <v/>
       </c>
       <c r="S21">
@@ -4050,19 +4326,35 @@
         <f>IFERROR($T20+$R21/SUM($G$12:$G$21),0)</f>
         <v/>
       </c>
-      <c r="U21" s="99">
-        <f>IF($S21="A",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="V21" s="99">
-        <f>IF($S21="B",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="W21" s="99">
-        <f>IF($S21="C",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="X21">
+      <c r="U21" s="100">
+        <f>IFERROR($R21/SUM($G$12:$G$21),0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="100">
+        <f>IF($S21="A",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="W21" s="100">
+        <f>IF($S21="B",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="X21" s="100">
+        <f>IF($S21="C",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="Y21" s="100">
+        <f>IF($S21="A",$T21,NA())</f>
+        <v/>
+      </c>
+      <c r="Z21" s="100">
+        <f>IF(OR($S21="A",$S21="B"),$T21,NA())</f>
+        <v/>
+      </c>
+      <c r="AA21" s="100">
+        <f>$T21</f>
+        <v/>
+      </c>
+      <c r="AB21">
         <f>IFERROR($G21+(21-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4176,7 +4468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4193,15 +4485,19 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="12" customWidth="1" min="16" max="16"/>
-    <col hidden="1" width="12" customWidth="1" min="17" max="17"/>
-    <col hidden="1" width="12" customWidth="1" min="18" max="18"/>
-    <col hidden="1" width="12" customWidth="1" min="19" max="19"/>
-    <col hidden="1" width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="11" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="11" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="11" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="11" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
@@ -4505,20 +4801,40 @@
       </c>
       <c r="U11" s="97" t="inlineStr">
         <is>
-          <t>Classe A</t>
+          <t>% Individual</t>
         </is>
       </c>
       <c r="V11" s="97" t="inlineStr">
         <is>
-          <t>Classe B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="W11" s="97" t="inlineStr">
         <is>
-          <t>Classe C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X11" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y11" s="97" t="inlineStr">
+        <is>
+          <t>Banda A</t>
+        </is>
+      </c>
+      <c r="Z11" s="97" t="inlineStr">
+        <is>
+          <t>Banda B</t>
+        </is>
+      </c>
+      <c r="AA11" s="97" t="inlineStr">
+        <is>
+          <t>Banda C</t>
+        </is>
+      </c>
+      <c r="AB11" s="97" t="inlineStr">
         <is>
           <t>score</t>
         </is>
@@ -4564,11 +4880,11 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P12),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P12),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R12" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P12),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P12),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S12">
@@ -4579,19 +4895,35 @@
         <f>IFERROR($R12/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U12" s="99">
-        <f>IF($S12="A",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="V12" s="99">
-        <f>IF($S12="B",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="W12" s="99">
-        <f>IF($S12="C",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="X12">
+      <c r="U12" s="100">
+        <f>IFERROR($R12/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="100">
+        <f>IF($S12="A",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="W12" s="100">
+        <f>IF($S12="B",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="X12" s="100">
+        <f>IF($S12="C",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="Y12" s="100">
+        <f>IF($S12="A",$T12,NA())</f>
+        <v/>
+      </c>
+      <c r="Z12" s="100">
+        <f>IF(OR($S12="A",$S12="B"),$T12,NA())</f>
+        <v/>
+      </c>
+      <c r="AA12" s="100">
+        <f>$T12</f>
+        <v/>
+      </c>
+      <c r="AB12">
         <f>IFERROR($G12+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4636,11 +4968,11 @@
         <v>2</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P13),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P13),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R13" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P13),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P13),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S13">
@@ -4651,19 +4983,35 @@
         <f>IFERROR($T12+$R13/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U13" s="99">
-        <f>IF($S13="A",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="V13" s="99">
-        <f>IF($S13="B",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="W13" s="99">
-        <f>IF($S13="C",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="X13">
+      <c r="U13" s="100">
+        <f>IFERROR($R13/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V13" s="100">
+        <f>IF($S13="A",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="W13" s="100">
+        <f>IF($S13="B",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="X13" s="100">
+        <f>IF($S13="C",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="Y13" s="100">
+        <f>IF($S13="A",$T13,NA())</f>
+        <v/>
+      </c>
+      <c r="Z13" s="100">
+        <f>IF(OR($S13="A",$S13="B"),$T13,NA())</f>
+        <v/>
+      </c>
+      <c r="AA13" s="100">
+        <f>$T13</f>
+        <v/>
+      </c>
+      <c r="AB13">
         <f>IFERROR($G13+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4708,11 +5056,11 @@
         <v>3</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P14),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P14),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R14" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P14),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P14),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S14">
@@ -4723,19 +5071,35 @@
         <f>IFERROR($T13+$R14/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U14" s="99">
-        <f>IF($S14="A",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="V14" s="99">
-        <f>IF($S14="B",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="W14" s="99">
-        <f>IF($S14="C",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="X14">
+      <c r="U14" s="100">
+        <f>IFERROR($R14/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="100">
+        <f>IF($S14="A",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="W14" s="100">
+        <f>IF($S14="B",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="X14" s="100">
+        <f>IF($S14="C",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="Y14" s="100">
+        <f>IF($S14="A",$T14,NA())</f>
+        <v/>
+      </c>
+      <c r="Z14" s="100">
+        <f>IF(OR($S14="A",$S14="B"),$T14,NA())</f>
+        <v/>
+      </c>
+      <c r="AA14" s="100">
+        <f>$T14</f>
+        <v/>
+      </c>
+      <c r="AB14">
         <f>IFERROR($G14+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4780,11 +5144,11 @@
         <v>4</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P15),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P15),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R15" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P15),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P15),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S15">
@@ -4795,19 +5159,35 @@
         <f>IFERROR($T14+$R15/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U15" s="99">
-        <f>IF($S15="A",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="V15" s="99">
-        <f>IF($S15="B",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="W15" s="99">
-        <f>IF($S15="C",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="X15">
+      <c r="U15" s="100">
+        <f>IFERROR($R15/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="100">
+        <f>IF($S15="A",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="W15" s="100">
+        <f>IF($S15="B",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="X15" s="100">
+        <f>IF($S15="C",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="Y15" s="100">
+        <f>IF($S15="A",$T15,NA())</f>
+        <v/>
+      </c>
+      <c r="Z15" s="100">
+        <f>IF(OR($S15="A",$S15="B"),$T15,NA())</f>
+        <v/>
+      </c>
+      <c r="AA15" s="100">
+        <f>$T15</f>
+        <v/>
+      </c>
+      <c r="AB15">
         <f>IFERROR($G15+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4852,11 +5232,11 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P16),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P16),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R16" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P16),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P16),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S16">
@@ -4867,19 +5247,35 @@
         <f>IFERROR($T15+$R16/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U16" s="99">
-        <f>IF($S16="A",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="V16" s="99">
-        <f>IF($S16="B",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="W16" s="99">
-        <f>IF($S16="C",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="X16">
+      <c r="U16" s="100">
+        <f>IFERROR($R16/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="100">
+        <f>IF($S16="A",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="W16" s="100">
+        <f>IF($S16="B",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="X16" s="100">
+        <f>IF($S16="C",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="Y16" s="100">
+        <f>IF($S16="A",$T16,NA())</f>
+        <v/>
+      </c>
+      <c r="Z16" s="100">
+        <f>IF(OR($S16="A",$S16="B"),$T16,NA())</f>
+        <v/>
+      </c>
+      <c r="AA16" s="100">
+        <f>$T16</f>
+        <v/>
+      </c>
+      <c r="AB16">
         <f>IFERROR($G16+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4924,11 +5320,11 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P17),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P17),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R17" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P17),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P17),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S17">
@@ -4939,19 +5335,35 @@
         <f>IFERROR($T16+$R17/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U17" s="99">
-        <f>IF($S17="A",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="V17" s="99">
-        <f>IF($S17="B",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="W17" s="99">
-        <f>IF($S17="C",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="X17">
+      <c r="U17" s="100">
+        <f>IFERROR($R17/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="100">
+        <f>IF($S17="A",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="W17" s="100">
+        <f>IF($S17="B",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="X17" s="100">
+        <f>IF($S17="C",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="Y17" s="100">
+        <f>IF($S17="A",$T17,NA())</f>
+        <v/>
+      </c>
+      <c r="Z17" s="100">
+        <f>IF(OR($S17="A",$S17="B"),$T17,NA())</f>
+        <v/>
+      </c>
+      <c r="AA17" s="100">
+        <f>$T17</f>
+        <v/>
+      </c>
+      <c r="AB17">
         <f>IFERROR($G17+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -4996,11 +5408,11 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P18),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P18),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R18" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P18),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P18),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S18">
@@ -5011,19 +5423,35 @@
         <f>IFERROR($T17+$R18/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U18" s="99">
-        <f>IF($S18="A",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="V18" s="99">
-        <f>IF($S18="B",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="W18" s="99">
-        <f>IF($S18="C",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="X18">
+      <c r="U18" s="100">
+        <f>IFERROR($R18/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V18" s="100">
+        <f>IF($S18="A",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="W18" s="100">
+        <f>IF($S18="B",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="X18" s="100">
+        <f>IF($S18="C",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="Y18" s="100">
+        <f>IF($S18="A",$T18,NA())</f>
+        <v/>
+      </c>
+      <c r="Z18" s="100">
+        <f>IF(OR($S18="A",$S18="B"),$T18,NA())</f>
+        <v/>
+      </c>
+      <c r="AA18" s="100">
+        <f>$T18</f>
+        <v/>
+      </c>
+      <c r="AB18">
         <f>IFERROR($G18+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5068,11 +5496,11 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P19),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P19),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R19" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P19),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P19),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S19">
@@ -5083,19 +5511,35 @@
         <f>IFERROR($T18+$R19/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U19" s="99">
-        <f>IF($S19="A",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="V19" s="99">
-        <f>IF($S19="B",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="W19" s="99">
-        <f>IF($S19="C",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="X19">
+      <c r="U19" s="100">
+        <f>IFERROR($R19/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V19" s="100">
+        <f>IF($S19="A",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="W19" s="100">
+        <f>IF($S19="B",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="X19" s="100">
+        <f>IF($S19="C",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="Y19" s="100">
+        <f>IF($S19="A",$T19,NA())</f>
+        <v/>
+      </c>
+      <c r="Z19" s="100">
+        <f>IF(OR($S19="A",$S19="B"),$T19,NA())</f>
+        <v/>
+      </c>
+      <c r="AA19" s="100">
+        <f>$T19</f>
+        <v/>
+      </c>
+      <c r="AB19">
         <f>IFERROR($G19+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5140,11 +5584,11 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P20),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P20),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R20" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P20),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P20),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S20">
@@ -5155,19 +5599,35 @@
         <f>IFERROR($T19+$R20/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U20" s="99">
-        <f>IF($S20="A",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="V20" s="99">
-        <f>IF($S20="B",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="W20" s="99">
-        <f>IF($S20="C",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="X20">
+      <c r="U20" s="100">
+        <f>IFERROR($R20/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="100">
+        <f>IF($S20="A",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="W20" s="100">
+        <f>IF($S20="B",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="X20" s="100">
+        <f>IF($S20="C",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="Y20" s="100">
+        <f>IF($S20="A",$T20,NA())</f>
+        <v/>
+      </c>
+      <c r="Z20" s="100">
+        <f>IF(OR($S20="A",$S20="B"),$T20,NA())</f>
+        <v/>
+      </c>
+      <c r="AA20" s="100">
+        <f>$T20</f>
+        <v/>
+      </c>
+      <c r="AB20">
         <f>IFERROR($G20+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5212,11 +5672,11 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P21),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P21),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R21" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P21),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P21),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S21">
@@ -5227,19 +5687,35 @@
         <f>IFERROR($T20+$R21/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U21" s="99">
-        <f>IF($S21="A",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="V21" s="99">
-        <f>IF($S21="B",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="W21" s="99">
-        <f>IF($S21="C",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="X21">
+      <c r="U21" s="100">
+        <f>IFERROR($R21/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="100">
+        <f>IF($S21="A",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="W21" s="100">
+        <f>IF($S21="B",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="X21" s="100">
+        <f>IF($S21="C",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="Y21" s="100">
+        <f>IF($S21="A",$T21,NA())</f>
+        <v/>
+      </c>
+      <c r="Z21" s="100">
+        <f>IF(OR($S21="A",$S21="B"),$T21,NA())</f>
+        <v/>
+      </c>
+      <c r="AA21" s="100">
+        <f>$T21</f>
+        <v/>
+      </c>
+      <c r="AB21">
         <f>IFERROR($G21+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5284,11 +5760,11 @@
         <v>11</v>
       </c>
       <c r="Q22">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P22),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P22),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R22" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P22),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P22),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S22">
@@ -5299,19 +5775,35 @@
         <f>IFERROR($T21+$R22/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U22" s="99">
-        <f>IF($S22="A",$R22,NA())</f>
-        <v/>
-      </c>
-      <c r="V22" s="99">
-        <f>IF($S22="B",$R22,NA())</f>
-        <v/>
-      </c>
-      <c r="W22" s="99">
-        <f>IF($S22="C",$R22,NA())</f>
-        <v/>
-      </c>
-      <c r="X22">
+      <c r="U22" s="100">
+        <f>IFERROR($R22/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V22" s="100">
+        <f>IF($S22="A",$U22,NA())</f>
+        <v/>
+      </c>
+      <c r="W22" s="100">
+        <f>IF($S22="B",$U22,NA())</f>
+        <v/>
+      </c>
+      <c r="X22" s="100">
+        <f>IF($S22="C",$U22,NA())</f>
+        <v/>
+      </c>
+      <c r="Y22" s="100">
+        <f>IF($S22="A",$T22,NA())</f>
+        <v/>
+      </c>
+      <c r="Z22" s="100">
+        <f>IF(OR($S22="A",$S22="B"),$T22,NA())</f>
+        <v/>
+      </c>
+      <c r="AA22" s="100">
+        <f>$T22</f>
+        <v/>
+      </c>
+      <c r="AB22">
         <f>IFERROR($G22+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5356,11 +5848,11 @@
         <v>12</v>
       </c>
       <c r="Q23">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P23),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P23),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R23" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P23),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P23),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S23">
@@ -5371,19 +5863,35 @@
         <f>IFERROR($T22+$R23/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U23" s="99">
-        <f>IF($S23="A",$R23,NA())</f>
-        <v/>
-      </c>
-      <c r="V23" s="99">
-        <f>IF($S23="B",$R23,NA())</f>
-        <v/>
-      </c>
-      <c r="W23" s="99">
-        <f>IF($S23="C",$R23,NA())</f>
-        <v/>
-      </c>
-      <c r="X23">
+      <c r="U23" s="100">
+        <f>IFERROR($R23/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V23" s="100">
+        <f>IF($S23="A",$U23,NA())</f>
+        <v/>
+      </c>
+      <c r="W23" s="100">
+        <f>IF($S23="B",$U23,NA())</f>
+        <v/>
+      </c>
+      <c r="X23" s="100">
+        <f>IF($S23="C",$U23,NA())</f>
+        <v/>
+      </c>
+      <c r="Y23" s="100">
+        <f>IF($S23="A",$T23,NA())</f>
+        <v/>
+      </c>
+      <c r="Z23" s="100">
+        <f>IF(OR($S23="A",$S23="B"),$T23,NA())</f>
+        <v/>
+      </c>
+      <c r="AA23" s="100">
+        <f>$T23</f>
+        <v/>
+      </c>
+      <c r="AB23">
         <f>IFERROR($G23+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5428,11 +5936,11 @@
         <v>13</v>
       </c>
       <c r="Q24">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P24),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P24),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R24" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P24),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P24),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S24">
@@ -5443,19 +5951,35 @@
         <f>IFERROR($T23+$R24/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U24" s="99">
-        <f>IF($S24="A",$R24,NA())</f>
-        <v/>
-      </c>
-      <c r="V24" s="99">
-        <f>IF($S24="B",$R24,NA())</f>
-        <v/>
-      </c>
-      <c r="W24" s="99">
-        <f>IF($S24="C",$R24,NA())</f>
-        <v/>
-      </c>
-      <c r="X24">
+      <c r="U24" s="100">
+        <f>IFERROR($R24/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V24" s="100">
+        <f>IF($S24="A",$U24,NA())</f>
+        <v/>
+      </c>
+      <c r="W24" s="100">
+        <f>IF($S24="B",$U24,NA())</f>
+        <v/>
+      </c>
+      <c r="X24" s="100">
+        <f>IF($S24="C",$U24,NA())</f>
+        <v/>
+      </c>
+      <c r="Y24" s="100">
+        <f>IF($S24="A",$T24,NA())</f>
+        <v/>
+      </c>
+      <c r="Z24" s="100">
+        <f>IF(OR($S24="A",$S24="B"),$T24,NA())</f>
+        <v/>
+      </c>
+      <c r="AA24" s="100">
+        <f>$T24</f>
+        <v/>
+      </c>
+      <c r="AB24">
         <f>IFERROR($G24+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5500,11 +6024,11 @@
         <v>14</v>
       </c>
       <c r="Q25">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P25),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P25),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R25" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P25),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P25),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S25">
@@ -5515,19 +6039,35 @@
         <f>IFERROR($T24+$R25/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U25" s="99">
-        <f>IF($S25="A",$R25,NA())</f>
-        <v/>
-      </c>
-      <c r="V25" s="99">
-        <f>IF($S25="B",$R25,NA())</f>
-        <v/>
-      </c>
-      <c r="W25" s="99">
-        <f>IF($S25="C",$R25,NA())</f>
-        <v/>
-      </c>
-      <c r="X25">
+      <c r="U25" s="100">
+        <f>IFERROR($R25/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V25" s="100">
+        <f>IF($S25="A",$U25,NA())</f>
+        <v/>
+      </c>
+      <c r="W25" s="100">
+        <f>IF($S25="B",$U25,NA())</f>
+        <v/>
+      </c>
+      <c r="X25" s="100">
+        <f>IF($S25="C",$U25,NA())</f>
+        <v/>
+      </c>
+      <c r="Y25" s="100">
+        <f>IF($S25="A",$T25,NA())</f>
+        <v/>
+      </c>
+      <c r="Z25" s="100">
+        <f>IF(OR($S25="A",$S25="B"),$T25,NA())</f>
+        <v/>
+      </c>
+      <c r="AA25" s="100">
+        <f>$T25</f>
+        <v/>
+      </c>
+      <c r="AB25">
         <f>IFERROR($G25+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5572,11 +6112,11 @@
         <v>15</v>
       </c>
       <c r="Q26">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P26),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P26),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R26" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P26),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P26),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S26">
@@ -5587,19 +6127,35 @@
         <f>IFERROR($T25+$R26/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U26" s="99">
-        <f>IF($S26="A",$R26,NA())</f>
-        <v/>
-      </c>
-      <c r="V26" s="99">
-        <f>IF($S26="B",$R26,NA())</f>
-        <v/>
-      </c>
-      <c r="W26" s="99">
-        <f>IF($S26="C",$R26,NA())</f>
-        <v/>
-      </c>
-      <c r="X26">
+      <c r="U26" s="100">
+        <f>IFERROR($R26/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V26" s="100">
+        <f>IF($S26="A",$U26,NA())</f>
+        <v/>
+      </c>
+      <c r="W26" s="100">
+        <f>IF($S26="B",$U26,NA())</f>
+        <v/>
+      </c>
+      <c r="X26" s="100">
+        <f>IF($S26="C",$U26,NA())</f>
+        <v/>
+      </c>
+      <c r="Y26" s="100">
+        <f>IF($S26="A",$T26,NA())</f>
+        <v/>
+      </c>
+      <c r="Z26" s="100">
+        <f>IF(OR($S26="A",$S26="B"),$T26,NA())</f>
+        <v/>
+      </c>
+      <c r="AA26" s="100">
+        <f>$T26</f>
+        <v/>
+      </c>
+      <c r="AB26">
         <f>IFERROR($G26+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5644,11 +6200,11 @@
         <v>16</v>
       </c>
       <c r="Q27">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P27),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P27),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R27" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P27),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P27),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S27">
@@ -5659,19 +6215,35 @@
         <f>IFERROR($T26+$R27/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U27" s="99">
-        <f>IF($S27="A",$R27,NA())</f>
-        <v/>
-      </c>
-      <c r="V27" s="99">
-        <f>IF($S27="B",$R27,NA())</f>
-        <v/>
-      </c>
-      <c r="W27" s="99">
-        <f>IF($S27="C",$R27,NA())</f>
-        <v/>
-      </c>
-      <c r="X27">
+      <c r="U27" s="100">
+        <f>IFERROR($R27/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V27" s="100">
+        <f>IF($S27="A",$U27,NA())</f>
+        <v/>
+      </c>
+      <c r="W27" s="100">
+        <f>IF($S27="B",$U27,NA())</f>
+        <v/>
+      </c>
+      <c r="X27" s="100">
+        <f>IF($S27="C",$U27,NA())</f>
+        <v/>
+      </c>
+      <c r="Y27" s="100">
+        <f>IF($S27="A",$T27,NA())</f>
+        <v/>
+      </c>
+      <c r="Z27" s="100">
+        <f>IF(OR($S27="A",$S27="B"),$T27,NA())</f>
+        <v/>
+      </c>
+      <c r="AA27" s="100">
+        <f>$T27</f>
+        <v/>
+      </c>
+      <c r="AB27">
         <f>IFERROR($G27+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5716,11 +6288,11 @@
         <v>17</v>
       </c>
       <c r="Q28">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P28),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P28),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R28" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P28),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P28),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S28">
@@ -5731,19 +6303,35 @@
         <f>IFERROR($T27+$R28/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U28" s="99">
-        <f>IF($S28="A",$R28,NA())</f>
-        <v/>
-      </c>
-      <c r="V28" s="99">
-        <f>IF($S28="B",$R28,NA())</f>
-        <v/>
-      </c>
-      <c r="W28" s="99">
-        <f>IF($S28="C",$R28,NA())</f>
-        <v/>
-      </c>
-      <c r="X28">
+      <c r="U28" s="100">
+        <f>IFERROR($R28/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V28" s="100">
+        <f>IF($S28="A",$U28,NA())</f>
+        <v/>
+      </c>
+      <c r="W28" s="100">
+        <f>IF($S28="B",$U28,NA())</f>
+        <v/>
+      </c>
+      <c r="X28" s="100">
+        <f>IF($S28="C",$U28,NA())</f>
+        <v/>
+      </c>
+      <c r="Y28" s="100">
+        <f>IF($S28="A",$T28,NA())</f>
+        <v/>
+      </c>
+      <c r="Z28" s="100">
+        <f>IF(OR($S28="A",$S28="B"),$T28,NA())</f>
+        <v/>
+      </c>
+      <c r="AA28" s="100">
+        <f>$T28</f>
+        <v/>
+      </c>
+      <c r="AB28">
         <f>IFERROR($G28+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5788,11 +6376,11 @@
         <v>18</v>
       </c>
       <c r="Q29">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P29),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P29),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R29" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P29),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P29),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S29">
@@ -5803,19 +6391,35 @@
         <f>IFERROR($T28+$R29/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U29" s="99">
-        <f>IF($S29="A",$R29,NA())</f>
-        <v/>
-      </c>
-      <c r="V29" s="99">
-        <f>IF($S29="B",$R29,NA())</f>
-        <v/>
-      </c>
-      <c r="W29" s="99">
-        <f>IF($S29="C",$R29,NA())</f>
-        <v/>
-      </c>
-      <c r="X29">
+      <c r="U29" s="100">
+        <f>IFERROR($R29/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V29" s="100">
+        <f>IF($S29="A",$U29,NA())</f>
+        <v/>
+      </c>
+      <c r="W29" s="100">
+        <f>IF($S29="B",$U29,NA())</f>
+        <v/>
+      </c>
+      <c r="X29" s="100">
+        <f>IF($S29="C",$U29,NA())</f>
+        <v/>
+      </c>
+      <c r="Y29" s="100">
+        <f>IF($S29="A",$T29,NA())</f>
+        <v/>
+      </c>
+      <c r="Z29" s="100">
+        <f>IF(OR($S29="A",$S29="B"),$T29,NA())</f>
+        <v/>
+      </c>
+      <c r="AA29" s="100">
+        <f>$T29</f>
+        <v/>
+      </c>
+      <c r="AB29">
         <f>IFERROR($G29+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5860,11 +6464,11 @@
         <v>19</v>
       </c>
       <c r="Q30">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P30),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P30),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R30" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P30),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P30),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S30">
@@ -5875,19 +6479,35 @@
         <f>IFERROR($T29+$R30/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U30" s="99">
-        <f>IF($S30="A",$R30,NA())</f>
-        <v/>
-      </c>
-      <c r="V30" s="99">
-        <f>IF($S30="B",$R30,NA())</f>
-        <v/>
-      </c>
-      <c r="W30" s="99">
-        <f>IF($S30="C",$R30,NA())</f>
-        <v/>
-      </c>
-      <c r="X30">
+      <c r="U30" s="100">
+        <f>IFERROR($R30/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V30" s="100">
+        <f>IF($S30="A",$U30,NA())</f>
+        <v/>
+      </c>
+      <c r="W30" s="100">
+        <f>IF($S30="B",$U30,NA())</f>
+        <v/>
+      </c>
+      <c r="X30" s="100">
+        <f>IF($S30="C",$U30,NA())</f>
+        <v/>
+      </c>
+      <c r="Y30" s="100">
+        <f>IF($S30="A",$T30,NA())</f>
+        <v/>
+      </c>
+      <c r="Z30" s="100">
+        <f>IF(OR($S30="A",$S30="B"),$T30,NA())</f>
+        <v/>
+      </c>
+      <c r="AA30" s="100">
+        <f>$T30</f>
+        <v/>
+      </c>
+      <c r="AB30">
         <f>IFERROR($G30+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -5932,11 +6552,11 @@
         <v>20</v>
       </c>
       <c r="Q31">
-        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($X$12:$X$31,$P31),$X$12:$X$31,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$31,MATCH(LARGE($AB$12:$AB$31,$P31),$AB$12:$AB$31,0)),"")</f>
         <v/>
       </c>
       <c r="R31" s="99">
-        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($X$12:$X$31,$P31),$X$12:$X$31,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$31,MATCH(LARGE($AB$12:$AB$31,$P31),$AB$12:$AB$31,0)),0)</f>
         <v/>
       </c>
       <c r="S31">
@@ -5947,19 +6567,35 @@
         <f>IFERROR($T30+$R31/SUM($G$12:$G$31),0)</f>
         <v/>
       </c>
-      <c r="U31" s="99">
-        <f>IF($S31="A",$R31,NA())</f>
-        <v/>
-      </c>
-      <c r="V31" s="99">
-        <f>IF($S31="B",$R31,NA())</f>
-        <v/>
-      </c>
-      <c r="W31" s="99">
-        <f>IF($S31="C",$R31,NA())</f>
-        <v/>
-      </c>
-      <c r="X31">
+      <c r="U31" s="100">
+        <f>IFERROR($R31/SUM($G$12:$G$31),0)</f>
+        <v/>
+      </c>
+      <c r="V31" s="100">
+        <f>IF($S31="A",$U31,NA())</f>
+        <v/>
+      </c>
+      <c r="W31" s="100">
+        <f>IF($S31="B",$U31,NA())</f>
+        <v/>
+      </c>
+      <c r="X31" s="100">
+        <f>IF($S31="C",$U31,NA())</f>
+        <v/>
+      </c>
+      <c r="Y31" s="100">
+        <f>IF($S31="A",$T31,NA())</f>
+        <v/>
+      </c>
+      <c r="Z31" s="100">
+        <f>IF(OR($S31="A",$S31="B"),$T31,NA())</f>
+        <v/>
+      </c>
+      <c r="AA31" s="100">
+        <f>$T31</f>
+        <v/>
+      </c>
+      <c r="AB31">
         <f>IFERROR($G31+(31-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6073,7 +6709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X42"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6090,15 +6726,19 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col hidden="1" width="12" customWidth="1" min="16" max="16"/>
-    <col hidden="1" width="12" customWidth="1" min="17" max="17"/>
-    <col hidden="1" width="12" customWidth="1" min="18" max="18"/>
-    <col hidden="1" width="12" customWidth="1" min="19" max="19"/>
-    <col hidden="1" width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="11" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="11" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="11" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="11" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1" ht="52" customHeight="1">
@@ -6402,20 +7042,40 @@
       </c>
       <c r="U11" s="97" t="inlineStr">
         <is>
-          <t>Classe A</t>
+          <t>% Individual</t>
         </is>
       </c>
       <c r="V11" s="97" t="inlineStr">
         <is>
-          <t>Classe B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="W11" s="97" t="inlineStr">
         <is>
-          <t>Classe C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X11" s="97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y11" s="97" t="inlineStr">
+        <is>
+          <t>Banda A</t>
+        </is>
+      </c>
+      <c r="Z11" s="97" t="inlineStr">
+        <is>
+          <t>Banda B</t>
+        </is>
+      </c>
+      <c r="AA11" s="97" t="inlineStr">
+        <is>
+          <t>Banda C</t>
+        </is>
+      </c>
+      <c r="AB11" s="97" t="inlineStr">
         <is>
           <t>score</t>
         </is>
@@ -6461,11 +7121,11 @@
         <v>1</v>
       </c>
       <c r="Q12">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P12),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P12),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R12" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P12),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P12),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S12">
@@ -6476,19 +7136,35 @@
         <f>IFERROR($R12/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U12" s="99">
-        <f>IF($S12="A",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="V12" s="99">
-        <f>IF($S12="B",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="W12" s="99">
-        <f>IF($S12="C",$R12,NA())</f>
-        <v/>
-      </c>
-      <c r="X12">
+      <c r="U12" s="100">
+        <f>IFERROR($R12/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V12" s="100">
+        <f>IF($S12="A",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="W12" s="100">
+        <f>IF($S12="B",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="X12" s="100">
+        <f>IF($S12="C",$U12,NA())</f>
+        <v/>
+      </c>
+      <c r="Y12" s="100">
+        <f>IF($S12="A",$T12,NA())</f>
+        <v/>
+      </c>
+      <c r="Z12" s="100">
+        <f>IF(OR($S12="A",$S12="B"),$T12,NA())</f>
+        <v/>
+      </c>
+      <c r="AA12" s="100">
+        <f>$T12</f>
+        <v/>
+      </c>
+      <c r="AB12">
         <f>IFERROR($G12+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6533,11 +7209,11 @@
         <v>2</v>
       </c>
       <c r="Q13">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P13),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P13),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R13" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P13),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P13),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S13">
@@ -6548,19 +7224,35 @@
         <f>IFERROR($T12+$R13/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U13" s="99">
-        <f>IF($S13="A",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="V13" s="99">
-        <f>IF($S13="B",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="W13" s="99">
-        <f>IF($S13="C",$R13,NA())</f>
-        <v/>
-      </c>
-      <c r="X13">
+      <c r="U13" s="100">
+        <f>IFERROR($R13/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V13" s="100">
+        <f>IF($S13="A",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="W13" s="100">
+        <f>IF($S13="B",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="X13" s="100">
+        <f>IF($S13="C",$U13,NA())</f>
+        <v/>
+      </c>
+      <c r="Y13" s="100">
+        <f>IF($S13="A",$T13,NA())</f>
+        <v/>
+      </c>
+      <c r="Z13" s="100">
+        <f>IF(OR($S13="A",$S13="B"),$T13,NA())</f>
+        <v/>
+      </c>
+      <c r="AA13" s="100">
+        <f>$T13</f>
+        <v/>
+      </c>
+      <c r="AB13">
         <f>IFERROR($G13+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6605,11 +7297,11 @@
         <v>3</v>
       </c>
       <c r="Q14">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P14),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P14),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R14" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P14),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P14),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S14">
@@ -6620,19 +7312,35 @@
         <f>IFERROR($T13+$R14/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U14" s="99">
-        <f>IF($S14="A",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="V14" s="99">
-        <f>IF($S14="B",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="W14" s="99">
-        <f>IF($S14="C",$R14,NA())</f>
-        <v/>
-      </c>
-      <c r="X14">
+      <c r="U14" s="100">
+        <f>IFERROR($R14/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V14" s="100">
+        <f>IF($S14="A",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="W14" s="100">
+        <f>IF($S14="B",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="X14" s="100">
+        <f>IF($S14="C",$U14,NA())</f>
+        <v/>
+      </c>
+      <c r="Y14" s="100">
+        <f>IF($S14="A",$T14,NA())</f>
+        <v/>
+      </c>
+      <c r="Z14" s="100">
+        <f>IF(OR($S14="A",$S14="B"),$T14,NA())</f>
+        <v/>
+      </c>
+      <c r="AA14" s="100">
+        <f>$T14</f>
+        <v/>
+      </c>
+      <c r="AB14">
         <f>IFERROR($G14+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6677,11 +7385,11 @@
         <v>4</v>
       </c>
       <c r="Q15">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P15),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P15),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R15" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P15),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P15),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S15">
@@ -6692,19 +7400,35 @@
         <f>IFERROR($T14+$R15/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U15" s="99">
-        <f>IF($S15="A",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="V15" s="99">
-        <f>IF($S15="B",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="W15" s="99">
-        <f>IF($S15="C",$R15,NA())</f>
-        <v/>
-      </c>
-      <c r="X15">
+      <c r="U15" s="100">
+        <f>IFERROR($R15/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V15" s="100">
+        <f>IF($S15="A",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="W15" s="100">
+        <f>IF($S15="B",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="X15" s="100">
+        <f>IF($S15="C",$U15,NA())</f>
+        <v/>
+      </c>
+      <c r="Y15" s="100">
+        <f>IF($S15="A",$T15,NA())</f>
+        <v/>
+      </c>
+      <c r="Z15" s="100">
+        <f>IF(OR($S15="A",$S15="B"),$T15,NA())</f>
+        <v/>
+      </c>
+      <c r="AA15" s="100">
+        <f>$T15</f>
+        <v/>
+      </c>
+      <c r="AB15">
         <f>IFERROR($G15+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6749,11 +7473,11 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P16),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P16),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R16" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P16),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P16),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S16">
@@ -6764,19 +7488,35 @@
         <f>IFERROR($T15+$R16/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U16" s="99">
-        <f>IF($S16="A",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="V16" s="99">
-        <f>IF($S16="B",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="W16" s="99">
-        <f>IF($S16="C",$R16,NA())</f>
-        <v/>
-      </c>
-      <c r="X16">
+      <c r="U16" s="100">
+        <f>IFERROR($R16/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V16" s="100">
+        <f>IF($S16="A",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="W16" s="100">
+        <f>IF($S16="B",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="X16" s="100">
+        <f>IF($S16="C",$U16,NA())</f>
+        <v/>
+      </c>
+      <c r="Y16" s="100">
+        <f>IF($S16="A",$T16,NA())</f>
+        <v/>
+      </c>
+      <c r="Z16" s="100">
+        <f>IF(OR($S16="A",$S16="B"),$T16,NA())</f>
+        <v/>
+      </c>
+      <c r="AA16" s="100">
+        <f>$T16</f>
+        <v/>
+      </c>
+      <c r="AB16">
         <f>IFERROR($G16+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6821,11 +7561,11 @@
         <v>6</v>
       </c>
       <c r="Q17">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P17),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P17),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R17" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P17),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P17),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S17">
@@ -6836,19 +7576,35 @@
         <f>IFERROR($T16+$R17/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U17" s="99">
-        <f>IF($S17="A",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="V17" s="99">
-        <f>IF($S17="B",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="W17" s="99">
-        <f>IF($S17="C",$R17,NA())</f>
-        <v/>
-      </c>
-      <c r="X17">
+      <c r="U17" s="100">
+        <f>IFERROR($R17/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V17" s="100">
+        <f>IF($S17="A",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="W17" s="100">
+        <f>IF($S17="B",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="X17" s="100">
+        <f>IF($S17="C",$U17,NA())</f>
+        <v/>
+      </c>
+      <c r="Y17" s="100">
+        <f>IF($S17="A",$T17,NA())</f>
+        <v/>
+      </c>
+      <c r="Z17" s="100">
+        <f>IF(OR($S17="A",$S17="B"),$T17,NA())</f>
+        <v/>
+      </c>
+      <c r="AA17" s="100">
+        <f>$T17</f>
+        <v/>
+      </c>
+      <c r="AB17">
         <f>IFERROR($G17+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6893,11 +7649,11 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P18),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P18),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R18" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P18),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P18),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S18">
@@ -6908,19 +7664,35 @@
         <f>IFERROR($T17+$R18/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U18" s="99">
-        <f>IF($S18="A",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="V18" s="99">
-        <f>IF($S18="B",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="W18" s="99">
-        <f>IF($S18="C",$R18,NA())</f>
-        <v/>
-      </c>
-      <c r="X18">
+      <c r="U18" s="100">
+        <f>IFERROR($R18/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V18" s="100">
+        <f>IF($S18="A",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="W18" s="100">
+        <f>IF($S18="B",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="X18" s="100">
+        <f>IF($S18="C",$U18,NA())</f>
+        <v/>
+      </c>
+      <c r="Y18" s="100">
+        <f>IF($S18="A",$T18,NA())</f>
+        <v/>
+      </c>
+      <c r="Z18" s="100">
+        <f>IF(OR($S18="A",$S18="B"),$T18,NA())</f>
+        <v/>
+      </c>
+      <c r="AA18" s="100">
+        <f>$T18</f>
+        <v/>
+      </c>
+      <c r="AB18">
         <f>IFERROR($G18+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -6965,11 +7737,11 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P19),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P19),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R19" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P19),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P19),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S19">
@@ -6980,19 +7752,35 @@
         <f>IFERROR($T18+$R19/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U19" s="99">
-        <f>IF($S19="A",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="V19" s="99">
-        <f>IF($S19="B",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="W19" s="99">
-        <f>IF($S19="C",$R19,NA())</f>
-        <v/>
-      </c>
-      <c r="X19">
+      <c r="U19" s="100">
+        <f>IFERROR($R19/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V19" s="100">
+        <f>IF($S19="A",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="W19" s="100">
+        <f>IF($S19="B",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="X19" s="100">
+        <f>IF($S19="C",$U19,NA())</f>
+        <v/>
+      </c>
+      <c r="Y19" s="100">
+        <f>IF($S19="A",$T19,NA())</f>
+        <v/>
+      </c>
+      <c r="Z19" s="100">
+        <f>IF(OR($S19="A",$S19="B"),$T19,NA())</f>
+        <v/>
+      </c>
+      <c r="AA19" s="100">
+        <f>$T19</f>
+        <v/>
+      </c>
+      <c r="AB19">
         <f>IFERROR($G19+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7037,11 +7825,11 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P20),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P20),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R20" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P20),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P20),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S20">
@@ -7052,19 +7840,35 @@
         <f>IFERROR($T19+$R20/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U20" s="99">
-        <f>IF($S20="A",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="V20" s="99">
-        <f>IF($S20="B",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="W20" s="99">
-        <f>IF($S20="C",$R20,NA())</f>
-        <v/>
-      </c>
-      <c r="X20">
+      <c r="U20" s="100">
+        <f>IFERROR($R20/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V20" s="100">
+        <f>IF($S20="A",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="W20" s="100">
+        <f>IF($S20="B",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="X20" s="100">
+        <f>IF($S20="C",$U20,NA())</f>
+        <v/>
+      </c>
+      <c r="Y20" s="100">
+        <f>IF($S20="A",$T20,NA())</f>
+        <v/>
+      </c>
+      <c r="Z20" s="100">
+        <f>IF(OR($S20="A",$S20="B"),$T20,NA())</f>
+        <v/>
+      </c>
+      <c r="AA20" s="100">
+        <f>$T20</f>
+        <v/>
+      </c>
+      <c r="AB20">
         <f>IFERROR($G20+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7109,11 +7913,11 @@
         <v>10</v>
       </c>
       <c r="Q21">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P21),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P21),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R21" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P21),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P21),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S21">
@@ -7124,19 +7928,35 @@
         <f>IFERROR($T20+$R21/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U21" s="99">
-        <f>IF($S21="A",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="V21" s="99">
-        <f>IF($S21="B",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="W21" s="99">
-        <f>IF($S21="C",$R21,NA())</f>
-        <v/>
-      </c>
-      <c r="X21">
+      <c r="U21" s="100">
+        <f>IFERROR($R21/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V21" s="100">
+        <f>IF($S21="A",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="W21" s="100">
+        <f>IF($S21="B",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="X21" s="100">
+        <f>IF($S21="C",$U21,NA())</f>
+        <v/>
+      </c>
+      <c r="Y21" s="100">
+        <f>IF($S21="A",$T21,NA())</f>
+        <v/>
+      </c>
+      <c r="Z21" s="100">
+        <f>IF(OR($S21="A",$S21="B"),$T21,NA())</f>
+        <v/>
+      </c>
+      <c r="AA21" s="100">
+        <f>$T21</f>
+        <v/>
+      </c>
+      <c r="AB21">
         <f>IFERROR($G21+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7181,11 +8001,11 @@
         <v>11</v>
       </c>
       <c r="Q22">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P22),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P22),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R22" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P22),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P22),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S22">
@@ -7196,19 +8016,35 @@
         <f>IFERROR($T21+$R22/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U22" s="99">
-        <f>IF($S22="A",$R22,NA())</f>
-        <v/>
-      </c>
-      <c r="V22" s="99">
-        <f>IF($S22="B",$R22,NA())</f>
-        <v/>
-      </c>
-      <c r="W22" s="99">
-        <f>IF($S22="C",$R22,NA())</f>
-        <v/>
-      </c>
-      <c r="X22">
+      <c r="U22" s="100">
+        <f>IFERROR($R22/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V22" s="100">
+        <f>IF($S22="A",$U22,NA())</f>
+        <v/>
+      </c>
+      <c r="W22" s="100">
+        <f>IF($S22="B",$U22,NA())</f>
+        <v/>
+      </c>
+      <c r="X22" s="100">
+        <f>IF($S22="C",$U22,NA())</f>
+        <v/>
+      </c>
+      <c r="Y22" s="100">
+        <f>IF($S22="A",$T22,NA())</f>
+        <v/>
+      </c>
+      <c r="Z22" s="100">
+        <f>IF(OR($S22="A",$S22="B"),$T22,NA())</f>
+        <v/>
+      </c>
+      <c r="AA22" s="100">
+        <f>$T22</f>
+        <v/>
+      </c>
+      <c r="AB22">
         <f>IFERROR($G22+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7253,11 +8089,11 @@
         <v>12</v>
       </c>
       <c r="Q23">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P23),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P23),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R23" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P23),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P23),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S23">
@@ -7268,19 +8104,35 @@
         <f>IFERROR($T22+$R23/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U23" s="99">
-        <f>IF($S23="A",$R23,NA())</f>
-        <v/>
-      </c>
-      <c r="V23" s="99">
-        <f>IF($S23="B",$R23,NA())</f>
-        <v/>
-      </c>
-      <c r="W23" s="99">
-        <f>IF($S23="C",$R23,NA())</f>
-        <v/>
-      </c>
-      <c r="X23">
+      <c r="U23" s="100">
+        <f>IFERROR($R23/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V23" s="100">
+        <f>IF($S23="A",$U23,NA())</f>
+        <v/>
+      </c>
+      <c r="W23" s="100">
+        <f>IF($S23="B",$U23,NA())</f>
+        <v/>
+      </c>
+      <c r="X23" s="100">
+        <f>IF($S23="C",$U23,NA())</f>
+        <v/>
+      </c>
+      <c r="Y23" s="100">
+        <f>IF($S23="A",$T23,NA())</f>
+        <v/>
+      </c>
+      <c r="Z23" s="100">
+        <f>IF(OR($S23="A",$S23="B"),$T23,NA())</f>
+        <v/>
+      </c>
+      <c r="AA23" s="100">
+        <f>$T23</f>
+        <v/>
+      </c>
+      <c r="AB23">
         <f>IFERROR($G23+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7325,11 +8177,11 @@
         <v>13</v>
       </c>
       <c r="Q24">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P24),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P24),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R24" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P24),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P24),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S24">
@@ -7340,19 +8192,35 @@
         <f>IFERROR($T23+$R24/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U24" s="99">
-        <f>IF($S24="A",$R24,NA())</f>
-        <v/>
-      </c>
-      <c r="V24" s="99">
-        <f>IF($S24="B",$R24,NA())</f>
-        <v/>
-      </c>
-      <c r="W24" s="99">
-        <f>IF($S24="C",$R24,NA())</f>
-        <v/>
-      </c>
-      <c r="X24">
+      <c r="U24" s="100">
+        <f>IFERROR($R24/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V24" s="100">
+        <f>IF($S24="A",$U24,NA())</f>
+        <v/>
+      </c>
+      <c r="W24" s="100">
+        <f>IF($S24="B",$U24,NA())</f>
+        <v/>
+      </c>
+      <c r="X24" s="100">
+        <f>IF($S24="C",$U24,NA())</f>
+        <v/>
+      </c>
+      <c r="Y24" s="100">
+        <f>IF($S24="A",$T24,NA())</f>
+        <v/>
+      </c>
+      <c r="Z24" s="100">
+        <f>IF(OR($S24="A",$S24="B"),$T24,NA())</f>
+        <v/>
+      </c>
+      <c r="AA24" s="100">
+        <f>$T24</f>
+        <v/>
+      </c>
+      <c r="AB24">
         <f>IFERROR($G24+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7397,11 +8265,11 @@
         <v>14</v>
       </c>
       <c r="Q25">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P25),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P25),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R25" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P25),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P25),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S25">
@@ -7412,19 +8280,35 @@
         <f>IFERROR($T24+$R25/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U25" s="99">
-        <f>IF($S25="A",$R25,NA())</f>
-        <v/>
-      </c>
-      <c r="V25" s="99">
-        <f>IF($S25="B",$R25,NA())</f>
-        <v/>
-      </c>
-      <c r="W25" s="99">
-        <f>IF($S25="C",$R25,NA())</f>
-        <v/>
-      </c>
-      <c r="X25">
+      <c r="U25" s="100">
+        <f>IFERROR($R25/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V25" s="100">
+        <f>IF($S25="A",$U25,NA())</f>
+        <v/>
+      </c>
+      <c r="W25" s="100">
+        <f>IF($S25="B",$U25,NA())</f>
+        <v/>
+      </c>
+      <c r="X25" s="100">
+        <f>IF($S25="C",$U25,NA())</f>
+        <v/>
+      </c>
+      <c r="Y25" s="100">
+        <f>IF($S25="A",$T25,NA())</f>
+        <v/>
+      </c>
+      <c r="Z25" s="100">
+        <f>IF(OR($S25="A",$S25="B"),$T25,NA())</f>
+        <v/>
+      </c>
+      <c r="AA25" s="100">
+        <f>$T25</f>
+        <v/>
+      </c>
+      <c r="AB25">
         <f>IFERROR($G25+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7469,11 +8353,11 @@
         <v>15</v>
       </c>
       <c r="Q26">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P26),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P26),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R26" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P26),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P26),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S26">
@@ -7484,19 +8368,35 @@
         <f>IFERROR($T25+$R26/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U26" s="99">
-        <f>IF($S26="A",$R26,NA())</f>
-        <v/>
-      </c>
-      <c r="V26" s="99">
-        <f>IF($S26="B",$R26,NA())</f>
-        <v/>
-      </c>
-      <c r="W26" s="99">
-        <f>IF($S26="C",$R26,NA())</f>
-        <v/>
-      </c>
-      <c r="X26">
+      <c r="U26" s="100">
+        <f>IFERROR($R26/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V26" s="100">
+        <f>IF($S26="A",$U26,NA())</f>
+        <v/>
+      </c>
+      <c r="W26" s="100">
+        <f>IF($S26="B",$U26,NA())</f>
+        <v/>
+      </c>
+      <c r="X26" s="100">
+        <f>IF($S26="C",$U26,NA())</f>
+        <v/>
+      </c>
+      <c r="Y26" s="100">
+        <f>IF($S26="A",$T26,NA())</f>
+        <v/>
+      </c>
+      <c r="Z26" s="100">
+        <f>IF(OR($S26="A",$S26="B"),$T26,NA())</f>
+        <v/>
+      </c>
+      <c r="AA26" s="100">
+        <f>$T26</f>
+        <v/>
+      </c>
+      <c r="AB26">
         <f>IFERROR($G26+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7541,11 +8441,11 @@
         <v>16</v>
       </c>
       <c r="Q27">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P27),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P27),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R27" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P27),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P27),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S27">
@@ -7556,19 +8456,35 @@
         <f>IFERROR($T26+$R27/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U27" s="99">
-        <f>IF($S27="A",$R27,NA())</f>
-        <v/>
-      </c>
-      <c r="V27" s="99">
-        <f>IF($S27="B",$R27,NA())</f>
-        <v/>
-      </c>
-      <c r="W27" s="99">
-        <f>IF($S27="C",$R27,NA())</f>
-        <v/>
-      </c>
-      <c r="X27">
+      <c r="U27" s="100">
+        <f>IFERROR($R27/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V27" s="100">
+        <f>IF($S27="A",$U27,NA())</f>
+        <v/>
+      </c>
+      <c r="W27" s="100">
+        <f>IF($S27="B",$U27,NA())</f>
+        <v/>
+      </c>
+      <c r="X27" s="100">
+        <f>IF($S27="C",$U27,NA())</f>
+        <v/>
+      </c>
+      <c r="Y27" s="100">
+        <f>IF($S27="A",$T27,NA())</f>
+        <v/>
+      </c>
+      <c r="Z27" s="100">
+        <f>IF(OR($S27="A",$S27="B"),$T27,NA())</f>
+        <v/>
+      </c>
+      <c r="AA27" s="100">
+        <f>$T27</f>
+        <v/>
+      </c>
+      <c r="AB27">
         <f>IFERROR($G27+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7613,11 +8529,11 @@
         <v>17</v>
       </c>
       <c r="Q28">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P28),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P28),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R28" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P28),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P28),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S28">
@@ -7628,19 +8544,35 @@
         <f>IFERROR($T27+$R28/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U28" s="99">
-        <f>IF($S28="A",$R28,NA())</f>
-        <v/>
-      </c>
-      <c r="V28" s="99">
-        <f>IF($S28="B",$R28,NA())</f>
-        <v/>
-      </c>
-      <c r="W28" s="99">
-        <f>IF($S28="C",$R28,NA())</f>
-        <v/>
-      </c>
-      <c r="X28">
+      <c r="U28" s="100">
+        <f>IFERROR($R28/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V28" s="100">
+        <f>IF($S28="A",$U28,NA())</f>
+        <v/>
+      </c>
+      <c r="W28" s="100">
+        <f>IF($S28="B",$U28,NA())</f>
+        <v/>
+      </c>
+      <c r="X28" s="100">
+        <f>IF($S28="C",$U28,NA())</f>
+        <v/>
+      </c>
+      <c r="Y28" s="100">
+        <f>IF($S28="A",$T28,NA())</f>
+        <v/>
+      </c>
+      <c r="Z28" s="100">
+        <f>IF(OR($S28="A",$S28="B"),$T28,NA())</f>
+        <v/>
+      </c>
+      <c r="AA28" s="100">
+        <f>$T28</f>
+        <v/>
+      </c>
+      <c r="AB28">
         <f>IFERROR($G28+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7685,11 +8617,11 @@
         <v>18</v>
       </c>
       <c r="Q29">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P29),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P29),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R29" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P29),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P29),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S29">
@@ -7700,19 +8632,35 @@
         <f>IFERROR($T28+$R29/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U29" s="99">
-        <f>IF($S29="A",$R29,NA())</f>
-        <v/>
-      </c>
-      <c r="V29" s="99">
-        <f>IF($S29="B",$R29,NA())</f>
-        <v/>
-      </c>
-      <c r="W29" s="99">
-        <f>IF($S29="C",$R29,NA())</f>
-        <v/>
-      </c>
-      <c r="X29">
+      <c r="U29" s="100">
+        <f>IFERROR($R29/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V29" s="100">
+        <f>IF($S29="A",$U29,NA())</f>
+        <v/>
+      </c>
+      <c r="W29" s="100">
+        <f>IF($S29="B",$U29,NA())</f>
+        <v/>
+      </c>
+      <c r="X29" s="100">
+        <f>IF($S29="C",$U29,NA())</f>
+        <v/>
+      </c>
+      <c r="Y29" s="100">
+        <f>IF($S29="A",$T29,NA())</f>
+        <v/>
+      </c>
+      <c r="Z29" s="100">
+        <f>IF(OR($S29="A",$S29="B"),$T29,NA())</f>
+        <v/>
+      </c>
+      <c r="AA29" s="100">
+        <f>$T29</f>
+        <v/>
+      </c>
+      <c r="AB29">
         <f>IFERROR($G29+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7757,11 +8705,11 @@
         <v>19</v>
       </c>
       <c r="Q30">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P30),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P30),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R30" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P30),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P30),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S30">
@@ -7772,19 +8720,35 @@
         <f>IFERROR($T29+$R30/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U30" s="99">
-        <f>IF($S30="A",$R30,NA())</f>
-        <v/>
-      </c>
-      <c r="V30" s="99">
-        <f>IF($S30="B",$R30,NA())</f>
-        <v/>
-      </c>
-      <c r="W30" s="99">
-        <f>IF($S30="C",$R30,NA())</f>
-        <v/>
-      </c>
-      <c r="X30">
+      <c r="U30" s="100">
+        <f>IFERROR($R30/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V30" s="100">
+        <f>IF($S30="A",$U30,NA())</f>
+        <v/>
+      </c>
+      <c r="W30" s="100">
+        <f>IF($S30="B",$U30,NA())</f>
+        <v/>
+      </c>
+      <c r="X30" s="100">
+        <f>IF($S30="C",$U30,NA())</f>
+        <v/>
+      </c>
+      <c r="Y30" s="100">
+        <f>IF($S30="A",$T30,NA())</f>
+        <v/>
+      </c>
+      <c r="Z30" s="100">
+        <f>IF(OR($S30="A",$S30="B"),$T30,NA())</f>
+        <v/>
+      </c>
+      <c r="AA30" s="100">
+        <f>$T30</f>
+        <v/>
+      </c>
+      <c r="AB30">
         <f>IFERROR($G30+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7829,11 +8793,11 @@
         <v>20</v>
       </c>
       <c r="Q31">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P31),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P31),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R31" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P31),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P31),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S31">
@@ -7844,19 +8808,35 @@
         <f>IFERROR($T30+$R31/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U31" s="99">
-        <f>IF($S31="A",$R31,NA())</f>
-        <v/>
-      </c>
-      <c r="V31" s="99">
-        <f>IF($S31="B",$R31,NA())</f>
-        <v/>
-      </c>
-      <c r="W31" s="99">
-        <f>IF($S31="C",$R31,NA())</f>
-        <v/>
-      </c>
-      <c r="X31">
+      <c r="U31" s="100">
+        <f>IFERROR($R31/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V31" s="100">
+        <f>IF($S31="A",$U31,NA())</f>
+        <v/>
+      </c>
+      <c r="W31" s="100">
+        <f>IF($S31="B",$U31,NA())</f>
+        <v/>
+      </c>
+      <c r="X31" s="100">
+        <f>IF($S31="C",$U31,NA())</f>
+        <v/>
+      </c>
+      <c r="Y31" s="100">
+        <f>IF($S31="A",$T31,NA())</f>
+        <v/>
+      </c>
+      <c r="Z31" s="100">
+        <f>IF(OR($S31="A",$S31="B"),$T31,NA())</f>
+        <v/>
+      </c>
+      <c r="AA31" s="100">
+        <f>$T31</f>
+        <v/>
+      </c>
+      <c r="AB31">
         <f>IFERROR($G31+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7901,11 +8881,11 @@
         <v>21</v>
       </c>
       <c r="Q32">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P32),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P32),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R32" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P32),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P32),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S32">
@@ -7916,19 +8896,35 @@
         <f>IFERROR($T31+$R32/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U32" s="99">
-        <f>IF($S32="A",$R32,NA())</f>
-        <v/>
-      </c>
-      <c r="V32" s="99">
-        <f>IF($S32="B",$R32,NA())</f>
-        <v/>
-      </c>
-      <c r="W32" s="99">
-        <f>IF($S32="C",$R32,NA())</f>
-        <v/>
-      </c>
-      <c r="X32">
+      <c r="U32" s="100">
+        <f>IFERROR($R32/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V32" s="100">
+        <f>IF($S32="A",$U32,NA())</f>
+        <v/>
+      </c>
+      <c r="W32" s="100">
+        <f>IF($S32="B",$U32,NA())</f>
+        <v/>
+      </c>
+      <c r="X32" s="100">
+        <f>IF($S32="C",$U32,NA())</f>
+        <v/>
+      </c>
+      <c r="Y32" s="100">
+        <f>IF($S32="A",$T32,NA())</f>
+        <v/>
+      </c>
+      <c r="Z32" s="100">
+        <f>IF(OR($S32="A",$S32="B"),$T32,NA())</f>
+        <v/>
+      </c>
+      <c r="AA32" s="100">
+        <f>$T32</f>
+        <v/>
+      </c>
+      <c r="AB32">
         <f>IFERROR($G32+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -7973,11 +8969,11 @@
         <v>22</v>
       </c>
       <c r="Q33">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P33),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P33),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R33" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P33),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P33),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S33">
@@ -7988,19 +8984,35 @@
         <f>IFERROR($T32+$R33/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U33" s="99">
-        <f>IF($S33="A",$R33,NA())</f>
-        <v/>
-      </c>
-      <c r="V33" s="99">
-        <f>IF($S33="B",$R33,NA())</f>
-        <v/>
-      </c>
-      <c r="W33" s="99">
-        <f>IF($S33="C",$R33,NA())</f>
-        <v/>
-      </c>
-      <c r="X33">
+      <c r="U33" s="100">
+        <f>IFERROR($R33/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V33" s="100">
+        <f>IF($S33="A",$U33,NA())</f>
+        <v/>
+      </c>
+      <c r="W33" s="100">
+        <f>IF($S33="B",$U33,NA())</f>
+        <v/>
+      </c>
+      <c r="X33" s="100">
+        <f>IF($S33="C",$U33,NA())</f>
+        <v/>
+      </c>
+      <c r="Y33" s="100">
+        <f>IF($S33="A",$T33,NA())</f>
+        <v/>
+      </c>
+      <c r="Z33" s="100">
+        <f>IF(OR($S33="A",$S33="B"),$T33,NA())</f>
+        <v/>
+      </c>
+      <c r="AA33" s="100">
+        <f>$T33</f>
+        <v/>
+      </c>
+      <c r="AB33">
         <f>IFERROR($G33+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8045,11 +9057,11 @@
         <v>23</v>
       </c>
       <c r="Q34">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P34),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P34),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R34" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P34),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P34),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S34">
@@ -8060,19 +9072,35 @@
         <f>IFERROR($T33+$R34/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U34" s="99">
-        <f>IF($S34="A",$R34,NA())</f>
-        <v/>
-      </c>
-      <c r="V34" s="99">
-        <f>IF($S34="B",$R34,NA())</f>
-        <v/>
-      </c>
-      <c r="W34" s="99">
-        <f>IF($S34="C",$R34,NA())</f>
-        <v/>
-      </c>
-      <c r="X34">
+      <c r="U34" s="100">
+        <f>IFERROR($R34/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V34" s="100">
+        <f>IF($S34="A",$U34,NA())</f>
+        <v/>
+      </c>
+      <c r="W34" s="100">
+        <f>IF($S34="B",$U34,NA())</f>
+        <v/>
+      </c>
+      <c r="X34" s="100">
+        <f>IF($S34="C",$U34,NA())</f>
+        <v/>
+      </c>
+      <c r="Y34" s="100">
+        <f>IF($S34="A",$T34,NA())</f>
+        <v/>
+      </c>
+      <c r="Z34" s="100">
+        <f>IF(OR($S34="A",$S34="B"),$T34,NA())</f>
+        <v/>
+      </c>
+      <c r="AA34" s="100">
+        <f>$T34</f>
+        <v/>
+      </c>
+      <c r="AB34">
         <f>IFERROR($G34+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8117,11 +9145,11 @@
         <v>24</v>
       </c>
       <c r="Q35">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P35),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P35),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R35" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P35),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P35),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S35">
@@ -8132,19 +9160,35 @@
         <f>IFERROR($T34+$R35/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U35" s="99">
-        <f>IF($S35="A",$R35,NA())</f>
-        <v/>
-      </c>
-      <c r="V35" s="99">
-        <f>IF($S35="B",$R35,NA())</f>
-        <v/>
-      </c>
-      <c r="W35" s="99">
-        <f>IF($S35="C",$R35,NA())</f>
-        <v/>
-      </c>
-      <c r="X35">
+      <c r="U35" s="100">
+        <f>IFERROR($R35/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V35" s="100">
+        <f>IF($S35="A",$U35,NA())</f>
+        <v/>
+      </c>
+      <c r="W35" s="100">
+        <f>IF($S35="B",$U35,NA())</f>
+        <v/>
+      </c>
+      <c r="X35" s="100">
+        <f>IF($S35="C",$U35,NA())</f>
+        <v/>
+      </c>
+      <c r="Y35" s="100">
+        <f>IF($S35="A",$T35,NA())</f>
+        <v/>
+      </c>
+      <c r="Z35" s="100">
+        <f>IF(OR($S35="A",$S35="B"),$T35,NA())</f>
+        <v/>
+      </c>
+      <c r="AA35" s="100">
+        <f>$T35</f>
+        <v/>
+      </c>
+      <c r="AB35">
         <f>IFERROR($G35+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8189,11 +9233,11 @@
         <v>25</v>
       </c>
       <c r="Q36">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P36),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P36),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R36" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P36),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P36),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S36">
@@ -8204,19 +9248,35 @@
         <f>IFERROR($T35+$R36/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U36" s="99">
-        <f>IF($S36="A",$R36,NA())</f>
-        <v/>
-      </c>
-      <c r="V36" s="99">
-        <f>IF($S36="B",$R36,NA())</f>
-        <v/>
-      </c>
-      <c r="W36" s="99">
-        <f>IF($S36="C",$R36,NA())</f>
-        <v/>
-      </c>
-      <c r="X36">
+      <c r="U36" s="100">
+        <f>IFERROR($R36/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V36" s="100">
+        <f>IF($S36="A",$U36,NA())</f>
+        <v/>
+      </c>
+      <c r="W36" s="100">
+        <f>IF($S36="B",$U36,NA())</f>
+        <v/>
+      </c>
+      <c r="X36" s="100">
+        <f>IF($S36="C",$U36,NA())</f>
+        <v/>
+      </c>
+      <c r="Y36" s="100">
+        <f>IF($S36="A",$T36,NA())</f>
+        <v/>
+      </c>
+      <c r="Z36" s="100">
+        <f>IF(OR($S36="A",$S36="B"),$T36,NA())</f>
+        <v/>
+      </c>
+      <c r="AA36" s="100">
+        <f>$T36</f>
+        <v/>
+      </c>
+      <c r="AB36">
         <f>IFERROR($G36+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8261,11 +9321,11 @@
         <v>26</v>
       </c>
       <c r="Q37">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P37),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P37),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R37" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P37),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P37),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S37">
@@ -8276,19 +9336,35 @@
         <f>IFERROR($T36+$R37/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U37" s="99">
-        <f>IF($S37="A",$R37,NA())</f>
-        <v/>
-      </c>
-      <c r="V37" s="99">
-        <f>IF($S37="B",$R37,NA())</f>
-        <v/>
-      </c>
-      <c r="W37" s="99">
-        <f>IF($S37="C",$R37,NA())</f>
-        <v/>
-      </c>
-      <c r="X37">
+      <c r="U37" s="100">
+        <f>IFERROR($R37/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V37" s="100">
+        <f>IF($S37="A",$U37,NA())</f>
+        <v/>
+      </c>
+      <c r="W37" s="100">
+        <f>IF($S37="B",$U37,NA())</f>
+        <v/>
+      </c>
+      <c r="X37" s="100">
+        <f>IF($S37="C",$U37,NA())</f>
+        <v/>
+      </c>
+      <c r="Y37" s="100">
+        <f>IF($S37="A",$T37,NA())</f>
+        <v/>
+      </c>
+      <c r="Z37" s="100">
+        <f>IF(OR($S37="A",$S37="B"),$T37,NA())</f>
+        <v/>
+      </c>
+      <c r="AA37" s="100">
+        <f>$T37</f>
+        <v/>
+      </c>
+      <c r="AB37">
         <f>IFERROR($G37+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8333,11 +9409,11 @@
         <v>27</v>
       </c>
       <c r="Q38">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P38),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P38),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R38" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P38),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P38),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S38">
@@ -8348,19 +9424,35 @@
         <f>IFERROR($T37+$R38/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U38" s="99">
-        <f>IF($S38="A",$R38,NA())</f>
-        <v/>
-      </c>
-      <c r="V38" s="99">
-        <f>IF($S38="B",$R38,NA())</f>
-        <v/>
-      </c>
-      <c r="W38" s="99">
-        <f>IF($S38="C",$R38,NA())</f>
-        <v/>
-      </c>
-      <c r="X38">
+      <c r="U38" s="100">
+        <f>IFERROR($R38/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V38" s="100">
+        <f>IF($S38="A",$U38,NA())</f>
+        <v/>
+      </c>
+      <c r="W38" s="100">
+        <f>IF($S38="B",$U38,NA())</f>
+        <v/>
+      </c>
+      <c r="X38" s="100">
+        <f>IF($S38="C",$U38,NA())</f>
+        <v/>
+      </c>
+      <c r="Y38" s="100">
+        <f>IF($S38="A",$T38,NA())</f>
+        <v/>
+      </c>
+      <c r="Z38" s="100">
+        <f>IF(OR($S38="A",$S38="B"),$T38,NA())</f>
+        <v/>
+      </c>
+      <c r="AA38" s="100">
+        <f>$T38</f>
+        <v/>
+      </c>
+      <c r="AB38">
         <f>IFERROR($G38+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8405,11 +9497,11 @@
         <v>28</v>
       </c>
       <c r="Q39">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P39),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P39),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R39" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P39),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P39),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S39">
@@ -8420,19 +9512,35 @@
         <f>IFERROR($T38+$R39/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U39" s="99">
-        <f>IF($S39="A",$R39,NA())</f>
-        <v/>
-      </c>
-      <c r="V39" s="99">
-        <f>IF($S39="B",$R39,NA())</f>
-        <v/>
-      </c>
-      <c r="W39" s="99">
-        <f>IF($S39="C",$R39,NA())</f>
-        <v/>
-      </c>
-      <c r="X39">
+      <c r="U39" s="100">
+        <f>IFERROR($R39/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V39" s="100">
+        <f>IF($S39="A",$U39,NA())</f>
+        <v/>
+      </c>
+      <c r="W39" s="100">
+        <f>IF($S39="B",$U39,NA())</f>
+        <v/>
+      </c>
+      <c r="X39" s="100">
+        <f>IF($S39="C",$U39,NA())</f>
+        <v/>
+      </c>
+      <c r="Y39" s="100">
+        <f>IF($S39="A",$T39,NA())</f>
+        <v/>
+      </c>
+      <c r="Z39" s="100">
+        <f>IF(OR($S39="A",$S39="B"),$T39,NA())</f>
+        <v/>
+      </c>
+      <c r="AA39" s="100">
+        <f>$T39</f>
+        <v/>
+      </c>
+      <c r="AB39">
         <f>IFERROR($G39+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8477,11 +9585,11 @@
         <v>29</v>
       </c>
       <c r="Q40">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P40),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P40),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R40" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P40),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P40),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S40">
@@ -8492,19 +9600,35 @@
         <f>IFERROR($T39+$R40/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U40" s="99">
-        <f>IF($S40="A",$R40,NA())</f>
-        <v/>
-      </c>
-      <c r="V40" s="99">
-        <f>IF($S40="B",$R40,NA())</f>
-        <v/>
-      </c>
-      <c r="W40" s="99">
-        <f>IF($S40="C",$R40,NA())</f>
-        <v/>
-      </c>
-      <c r="X40">
+      <c r="U40" s="100">
+        <f>IFERROR($R40/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V40" s="100">
+        <f>IF($S40="A",$U40,NA())</f>
+        <v/>
+      </c>
+      <c r="W40" s="100">
+        <f>IF($S40="B",$U40,NA())</f>
+        <v/>
+      </c>
+      <c r="X40" s="100">
+        <f>IF($S40="C",$U40,NA())</f>
+        <v/>
+      </c>
+      <c r="Y40" s="100">
+        <f>IF($S40="A",$T40,NA())</f>
+        <v/>
+      </c>
+      <c r="Z40" s="100">
+        <f>IF(OR($S40="A",$S40="B"),$T40,NA())</f>
+        <v/>
+      </c>
+      <c r="AA40" s="100">
+        <f>$T40</f>
+        <v/>
+      </c>
+      <c r="AB40">
         <f>IFERROR($G40+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>
@@ -8549,11 +9673,11 @@
         <v>30</v>
       </c>
       <c r="Q41">
-        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($X$12:$X$41,$P41),$X$12:$X$41,0)),"")</f>
+        <f>IFERROR(INDEX($B$12:$B$41,MATCH(LARGE($AB$12:$AB$41,$P41),$AB$12:$AB$41,0)),"")</f>
         <v/>
       </c>
       <c r="R41" s="99">
-        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($X$12:$X$41,$P41),$X$12:$X$41,0)),0)</f>
+        <f>IFERROR(INDEX($G$12:$G$41,MATCH(LARGE($AB$12:$AB$41,$P41),$AB$12:$AB$41,0)),0)</f>
         <v/>
       </c>
       <c r="S41">
@@ -8564,19 +9688,35 @@
         <f>IFERROR($T40+$R41/SUM($G$12:$G$41),0)</f>
         <v/>
       </c>
-      <c r="U41" s="99">
-        <f>IF($S41="A",$R41,NA())</f>
-        <v/>
-      </c>
-      <c r="V41" s="99">
-        <f>IF($S41="B",$R41,NA())</f>
-        <v/>
-      </c>
-      <c r="W41" s="99">
-        <f>IF($S41="C",$R41,NA())</f>
-        <v/>
-      </c>
-      <c r="X41">
+      <c r="U41" s="100">
+        <f>IFERROR($R41/SUM($G$12:$G$41),0)</f>
+        <v/>
+      </c>
+      <c r="V41" s="100">
+        <f>IF($S41="A",$U41,NA())</f>
+        <v/>
+      </c>
+      <c r="W41" s="100">
+        <f>IF($S41="B",$U41,NA())</f>
+        <v/>
+      </c>
+      <c r="X41" s="100">
+        <f>IF($S41="C",$U41,NA())</f>
+        <v/>
+      </c>
+      <c r="Y41" s="100">
+        <f>IF($S41="A",$T41,NA())</f>
+        <v/>
+      </c>
+      <c r="Z41" s="100">
+        <f>IF(OR($S41="A",$S41="B"),$T41,NA())</f>
+        <v/>
+      </c>
+      <c r="AA41" s="100">
+        <f>$T41</f>
+        <v/>
+      </c>
+      <c r="AB41">
         <f>IFERROR($G41+(41-ROW())/1000000000,0)</f>
         <v/>
       </c>

--- a/output/curva_abc_reggae_6.xlsx
+++ b/output/curva_abc_reggae_6.xlsx
@@ -2111,14 +2111,18 @@
     </comment>
     <comment ref="E12" authorId="1" shapeId="0">
       <text>
-        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.).
-V.T., % e Classe ABC sao recalculados automaticamente.</t>
+        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.) - elas estao
+desbloqueadas. V.T., % e Classe ABC recalculam automaticamente.
+Para desproteger a aba: Revisao -&gt; Desproteger Planilha
+Senha: reggae</t>
       </text>
     </comment>
     <comment ref="F12" authorId="1" shapeId="0">
       <text>
-        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.).
-V.T., % e Classe ABC sao recalculados automaticamente.</t>
+        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.) - elas estao
+desbloqueadas. V.T., % e Classe ABC recalculam automaticamente.
+Para desproteger a aba: Revisao -&gt; Desproteger Planilha
+Senha: reggae</t>
       </text>
     </comment>
   </commentList>
@@ -2148,14 +2152,18 @@
     </comment>
     <comment ref="E12" authorId="1" shapeId="0">
       <text>
-        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.).
-V.T., % e Classe ABC sao recalculados automaticamente.</t>
+        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.) - elas estao
+desbloqueadas. V.T., % e Classe ABC recalculam automaticamente.
+Para desproteger a aba: Revisao -&gt; Desproteger Planilha
+Senha: reggae</t>
       </text>
     </comment>
     <comment ref="F12" authorId="1" shapeId="0">
       <text>
-        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.).
-V.T., % e Classe ABC sao recalculados automaticamente.</t>
+        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.) - elas estao
+desbloqueadas. V.T., % e Classe ABC recalculam automaticamente.
+Para desproteger a aba: Revisao -&gt; Desproteger Planilha
+Senha: reggae</t>
       </text>
     </comment>
   </commentList>
@@ -2185,14 +2193,18 @@
     </comment>
     <comment ref="E12" authorId="1" shapeId="0">
       <text>
-        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.).
-V.T., % e Classe ABC sao recalculados automaticamente.</t>
+        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.) - elas estao
+desbloqueadas. V.T., % e Classe ABC recalculam automaticamente.
+Para desproteger a aba: Revisao -&gt; Desproteger Planilha
+Senha: reggae</t>
       </text>
     </comment>
     <comment ref="F12" authorId="1" shapeId="0">
       <text>
-        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.).
-V.T., % e Classe ABC sao recalculados automaticamente.</t>
+        <t>Edite apenas as colunas E (Qtd.) e F (Custo Unit.) - elas estao
+desbloqueadas. V.T., % e Classe ABC recalculam automaticamente.
+Para desproteger a aba: Revisao -&gt; Desproteger Planilha
+Senha: reggae</t>
       </text>
     </comment>
   </commentList>
@@ -3086,6 +3098,7 @@
       <c r="K43" s="75" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DF15"/>
   <mergeCells count="7">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B9:K9"/>
@@ -4386,7 +4399,7 @@
     </row>
     <row r="23" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DF15"/>
   <mergeCells count="21">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A22:D22"/>
@@ -6627,7 +6640,7 @@
     </row>
     <row r="33" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DF15"/>
   <mergeCells count="21">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C5:D5"/>
@@ -9748,7 +9761,7 @@
     </row>
     <row r="43" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="F0B1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DF15"/>
   <mergeCells count="21">
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C5:D5"/>
